--- a/docs/SECS/SECS_GEM功能_Handler_20260831.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260831.xlsx
@@ -5058,7 +5058,7 @@
     <row r="86">
       <c r="A86" s="43" t="inlineStr">
         <is>
-          <t>〔20260831 追加項：表尾註 (f)〕本版新增 6 個 SVID：66040-66045 AMR AUTO1-6 Lot Number，公布各出料流道當前負責分選的貨批批號，供 AMR 下貨流程辨識所收走的出料車屬於哪一批。⚠ 這六個號碼僅供 S1F3 / S1F11 查詢，不掛在任何事件報表——CEID 272 / 274 的報表內容與長度完全不變，貴端既有的報表解析不需修改。⚠ 本機自有的 66xxx 號段曾於 20260804 全數下架（見「修訂說明」頁），本次依貴端指示自 66040 起重新啟用；20260804 已下架的 66000-66039 各號永不挪用。</t>
+          <t>〔20260831 追加項：表尾註 (f)〕本版新增 6 個 SVID：66040-66045 AMR AUTO1-6 Lot Number，公布各出料流道當前負責分選的貨批批號，供 AMR 下貨流程辨識所收走的出料車屬於哪一批。⚠ 本方韌體內建的報表不掛這六個號碼，CEID 272 / 274 在未經貴端 S2F35 重新連結的預設狀態下，報表內容與長度完全不變；貴端若要在事件中一併取得，請自行以 S2F33 定義含這六號的 RPTID 再以 S2F35 連結——貴端現行的 RPTID 2001 即為此作法，2026-08-31 現場實測已正常帶出批號。⚠ 值的來源是「批號→出料流道」的動態綁定，僅在 By Lot+Bin / By Lot+PassFail 兩種分選模式、且該流道已被綁定時才有值；NORMAL 分選模式、尚未綁定、或該流道為 Error 流道時回零長度字串（零長度是正式值，不是錯誤）。綁定在 CCD 讀到 2D 並命中已宣告批號時建立，故 2D 讀取失敗期間這六個號碼都會是零長度。⚠ 本機自有的 66xxx 號段曾於 20260804 全數下架（見「修訂說明」頁），本次依貴端指示自 66040 起重新啟用；20260804 已下架的 66000-66039 各號永不挪用，日後擴充自 66046 往上。</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22768,7 @@
       </c>
       <c r="B3" s="54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-31（2026-09-01 措辭補充，號碼與語意未變）</t>
         </is>
       </c>
     </row>
@@ -22833,7 +22833,8 @@
 ‧ 取值來源＝(Lot,Bin)→Auto 綁定表，與主畫面下料區各站顯示的批號同源。
 ‧ By Lot+Bin 與 By Lot+PassFail 分選模式下有值；一般 Bin→Auto 靜態模式因無流道層的批號綁定，恆為零長度字串。
 ‧ 一個流道恆只對應一個批號。
-‧ 僅供 S1F3 / S1F11 查詢，不掛在任何事件報表上。</t>
+‧ 綁定於 CCD 讀到 2D 並命中已宣告批號時建立，故 2D 讀取失敗期間恆為零長度字串（零長度是正式值，不是錯誤）。
+‧ 本方韌體內建的報表不掛這六個號碼；貴端若自行以 S2F33 定義含這六號的 RPTID 再以 S2F35 連結，事件中即會帶出（貴端現行的 RPTID 2001 即為此作法）。</t>
         </is>
       </c>
     </row>
@@ -22845,8 +22846,10 @@
       </c>
       <c r="B9" s="54" t="inlineStr">
         <is>
-          <t>⚠ 本次新增的六個 SVID 刻意不加入報表 6（AMR 站別 Tray / Device Count）。CEID 272 AMR Supplement 與 CEID 274 AMR LDUnLD Finish 的報表內容、欄位順序與長度完全不變，貴端既有的 S6F11 解析不需要做任何修改。
-若貴端日後希望在下貨事件當下直接收到批號，請告知，本方會另開一個新的報表號掛上去，而不會加寬現有報表。</t>
+          <t>⚠ 本次新增的六個 SVID 刻意不加入本方韌體內建的報表 6（AMR 站別 Tray / Device Count）。CEID 272 AMR Supplement 與 CEID 274 AMR LDUnLD Finish 在未經貴端 S2F35 重新連結的預設狀態下，報表內容、欄位順序與長度完全不變，貴端既有的 S6F11 解析不需要做任何修改。
+〔2026-09-01 措辭補充〕本項原寫「不掛在任何事件報表」，該句僅指本方韌體內建的報表。貴端仍可自行以 S2F33 定義含這六號的 RPTID、再以 S2F35 連結到任一 CEID，事件中即會帶出。2026-08-31 現場即為此情形：貴端的 RPTID 2001 已含 66040-66045 並連結至 CEID 272，實測已正常帶出批號。
+⚠ 併此提醒 S2F35 的取代語意：S2F35 是「取代」該 CEID 的整組報表連結，不是疊加。貴端把 CEID 272 / 274 重新連結到自訂報表之後，本方韌體預設掛在這兩個事件上的報表 6（各站 Tray Count / Device Count）即被覆寫而不再送出。若需於下貨完成事件取得關帳盤數與 IC 數，請在該連結中一併帶入含 SVID 38222-38227 / 38246-38248（Tray Count）與 38228-38233 / 38240-38242（Device Count）的報表號，或直接把本方韌體內建的報表 6 加進連結（報表 6 為韌體內建，開機即存在，不需以 S2F33 定義）。
+⚠ 另請注意 S2F35 的連結不跨電源保存：復電後 CEID 272 / 274 會先退回本方韌體預設（帶報表 6），直到貴端重下 S2F35 才又被覆寫，故同一台機器在復電前後可能出現兩種 body 長度，這不是韌體不穩定。</t>
         </is>
       </c>
     </row>
@@ -22901,7 +22904,8 @@
       <c r="B13" s="54" t="inlineStr">
         <is>
           <t>‧ 66040-66045 的名稱字串（AMR AUTO1-6 Lot Number）若貴端 EAP 有既定命名慣例，請告知調整。
-‧ 是否需要在 CEID 272 / 274 之外，另以新報表號於下貨事件當下推送批號。</t>
+‧ 〔2026-09-01 更新〕原列「是否需要在 CEID 272 / 274 之外，另以新報表號於下貨事件當下推送批號」一項：2026-08-31 現場貴端已自行將 66040-66045 納入 RPTID 2001 並連結至 CEID 272，實測正常帶出，本方不需另開報表號。若貴端也希望在 CEID 274（下貨完成）取得批號，把同一個報表號加入 CEID 274 的 S2F35 連結即可，本方不需改韌體。
+‧ 〔2026-09-01 新增〕請確認貴端 CEID 273 / 274 的 S2F35 連結是否要補上含各站 Tray / Device Count 的報表號：2026-08-31 現場的連結為 {502, 2000}，本方韌體預設的報表 6 因而被覆寫，CEID 274 未帶關帳盤數與 IC 數。</t>
         </is>
       </c>
     </row>
